--- a/grupos/5BLCM - Estadisticos 20221.xlsx
+++ b/grupos/5BLCM - Estadisticos 20221.xlsx
@@ -962,10 +962,10 @@
         <v>7</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
         <v>-1</v>
@@ -977,7 +977,7 @@
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1001,7 +1001,7 @@
         <v>8</v>
       </c>
       <c r="U4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V4">
         <v>-1</v>
@@ -1039,13 +1039,13 @@
         <v>10</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
         <v>-1</v>
@@ -1054,7 +1054,7 @@
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1075,13 +1075,13 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U5">
         <v>9</v>
       </c>
       <c r="V5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W5">
         <v>9</v>
@@ -1116,10 +1116,10 @@
         <v>9</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
         <v>-1</v>
@@ -1131,7 +1131,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1152,7 +1152,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>8</v>
@@ -1167,7 +1167,7 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1193,13 +1193,13 @@
         <v>7</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K7">
         <v>-1</v>
@@ -1208,7 +1208,7 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1229,13 +1229,13 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U7">
         <v>7</v>
       </c>
       <c r="V7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W7">
         <v>6</v>
@@ -1244,7 +1244,7 @@
         <v>8</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1270,13 +1270,13 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
         <v>-1</v>
@@ -1285,7 +1285,7 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1306,10 +1306,10 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>8</v>
@@ -1347,13 +1347,13 @@
         <v>10</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
         <v>-1</v>
@@ -1362,7 +1362,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1424,13 +1424,13 @@
         <v>10</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K10">
         <v>-1</v>
@@ -1439,7 +1439,7 @@
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1460,10 +1460,10 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V10">
         <v>7</v>
@@ -1501,13 +1501,13 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K11">
         <v>-1</v>
@@ -1516,7 +1516,7 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1537,10 +1537,10 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V11">
         <v>8</v>
@@ -1578,13 +1578,13 @@
         <v>10</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
         <v>-1</v>
@@ -1593,7 +1593,7 @@
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1614,7 +1614,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U12">
         <v>9</v>
@@ -1655,13 +1655,13 @@
         <v>8</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
         <v>-1</v>
@@ -1670,7 +1670,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1697,7 +1697,7 @@
         <v>9</v>
       </c>
       <c r="V13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -1706,7 +1706,7 @@
         <v>9</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1732,10 +1732,10 @@
         <v>9</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J14">
         <v>-1</v>
@@ -1747,7 +1747,7 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1768,10 +1768,10 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>-1</v>
@@ -1783,7 +1783,7 @@
         <v>9</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1809,7 +1809,7 @@
         <v>9</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -1824,7 +1824,7 @@
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1845,7 +1845,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U15">
         <v>-1</v>
@@ -1886,13 +1886,13 @@
         <v>10</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
         <v>-1</v>
@@ -1901,7 +1901,7 @@
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1922,7 +1922,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U16">
         <v>9</v>
@@ -1963,10 +1963,10 @@
         <v>10</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
         <v>-1</v>
@@ -1978,7 +1978,7 @@
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1999,7 +1999,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U17">
         <v>7</v>
@@ -2040,13 +2040,13 @@
         <v>10</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K18">
         <v>-1</v>
@@ -2055,7 +2055,7 @@
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2076,7 +2076,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U18">
         <v>8</v>
@@ -2117,7 +2117,7 @@
         <v>10</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -2132,7 +2132,7 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2153,7 +2153,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U19">
         <v>7</v>
@@ -2194,13 +2194,13 @@
         <v>8</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K20">
         <v>-1</v>
@@ -2209,7 +2209,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2230,7 +2230,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -2245,7 +2245,7 @@
         <v>10</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2271,10 +2271,10 @@
         <v>9</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
         <v>-1</v>
@@ -2286,7 +2286,7 @@
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2307,10 +2307,10 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V21">
         <v>-1</v>
@@ -2322,7 +2322,7 @@
         <v>9</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2348,13 +2348,13 @@
         <v>10</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K22">
         <v>-1</v>
@@ -2363,7 +2363,7 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2384,13 +2384,13 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>7</v>
@@ -2425,13 +2425,13 @@
         <v>10</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I23">
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
         <v>-1</v>
@@ -2440,7 +2440,7 @@
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2461,7 +2461,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U23">
         <v>8</v>
@@ -2476,7 +2476,7 @@
         <v>10</v>
       </c>
       <c r="Y23">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2502,13 +2502,13 @@
         <v>7</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K24">
         <v>-1</v>
@@ -2517,7 +2517,7 @@
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2538,10 +2538,10 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V24">
         <v>7</v>
@@ -2553,7 +2553,7 @@
         <v>8</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2579,7 +2579,7 @@
         <v>8</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I25">
         <v>-1</v>
@@ -2594,7 +2594,7 @@
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2615,7 +2615,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U25">
         <v>7</v>
@@ -2656,13 +2656,13 @@
         <v>8</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K26">
         <v>-1</v>
@@ -2671,7 +2671,7 @@
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2692,13 +2692,13 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U26">
         <v>7</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>6</v>
@@ -2707,7 +2707,7 @@
         <v>5</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2733,10 +2733,10 @@
         <v>8</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J27">
         <v>-1</v>
@@ -2748,7 +2748,7 @@
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2769,10 +2769,10 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V27">
         <v>-1</v>
@@ -2784,7 +2784,7 @@
         <v>5</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2810,7 +2810,7 @@
         <v>9</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I28">
         <v>-1</v>
@@ -2825,7 +2825,7 @@
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2846,7 +2846,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U28">
         <v>6</v>
@@ -2861,7 +2861,7 @@
         <v>5</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2887,13 +2887,13 @@
         <v>10</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
         <v>-1</v>
@@ -2902,7 +2902,7 @@
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2923,7 +2923,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U29">
         <v>9</v>
@@ -2964,13 +2964,13 @@
         <v>7</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K30">
         <v>-1</v>
@@ -2979,7 +2979,7 @@
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3000,7 +3000,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U30">
         <v>8</v>
@@ -3015,7 +3015,7 @@
         <v>10</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3041,13 +3041,13 @@
         <v>8</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K31">
         <v>-1</v>
@@ -3056,7 +3056,7 @@
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3077,7 +3077,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U31">
         <v>9</v>
@@ -3092,7 +3092,7 @@
         <v>10</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3118,13 +3118,13 @@
         <v>7</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K32">
         <v>-1</v>
@@ -3133,7 +3133,7 @@
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3154,7 +3154,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U32">
         <v>7</v>
@@ -3169,7 +3169,7 @@
         <v>5</v>
       </c>
       <c r="Y32">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3195,13 +3195,13 @@
         <v>10</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K33">
         <v>-1</v>
@@ -3210,7 +3210,7 @@
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3234,7 +3234,7 @@
         <v>10</v>
       </c>
       <c r="U33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V33">
         <v>8</v>
@@ -3272,13 +3272,13 @@
         <v>10</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K34">
         <v>-1</v>
@@ -3287,7 +3287,7 @@
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3349,13 +3349,13 @@
         <v>10</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K35">
         <v>-1</v>
@@ -3364,7 +3364,7 @@
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3385,7 +3385,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U35">
         <v>9</v>
@@ -3477,7 +3477,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I2">
         <v>10</v>
@@ -3573,7 +3573,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -3605,7 +3605,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3637,7 +3637,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/5BLCM - Estadisticos 20221.xlsx
+++ b/grupos/5BLCM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="147">
   <si>
     <t>Materia</t>
   </si>
@@ -182,13 +182,13 @@
     <t>Ortega Valle Manuel</t>
   </si>
   <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
-    <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
     <t>Ángel Martínez Gerson Hermenegildo</t>
@@ -974,7 +974,7 @@
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M4">
         <v>7</v>
@@ -1010,7 +1010,7 @@
         <v>5</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y4">
         <v>7</v>
@@ -1051,7 +1051,7 @@
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
         <v>10</v>
@@ -1128,7 +1128,7 @@
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
         <v>10</v>
@@ -1164,7 +1164,7 @@
         <v>7</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y6">
         <v>10</v>
@@ -1205,7 +1205,7 @@
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
         <v>8</v>
@@ -1241,7 +1241,7 @@
         <v>6</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y7">
         <v>8</v>
@@ -1282,7 +1282,7 @@
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
         <v>10</v>
@@ -1359,7 +1359,7 @@
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
         <v>10</v>
@@ -1436,7 +1436,7 @@
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
         <v>10</v>
@@ -1513,7 +1513,7 @@
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
         <v>10</v>
@@ -1590,7 +1590,7 @@
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
         <v>10</v>
@@ -1667,7 +1667,7 @@
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
         <v>9</v>
@@ -1703,7 +1703,7 @@
         <v>8</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y13">
         <v>9</v>
@@ -1744,7 +1744,7 @@
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
         <v>10</v>
@@ -1780,7 +1780,7 @@
         <v>6</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y14">
         <v>10</v>
@@ -1821,7 +1821,7 @@
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
         <v>8</v>
@@ -1857,7 +1857,7 @@
         <v>6</v>
       </c>
       <c r="X15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y15">
         <v>9</v>
@@ -1898,7 +1898,7 @@
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
         <v>10</v>
@@ -1975,7 +1975,7 @@
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
         <v>10</v>
@@ -2011,7 +2011,7 @@
         <v>5</v>
       </c>
       <c r="X17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y17">
         <v>10</v>
@@ -2052,7 +2052,7 @@
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
         <v>10</v>
@@ -2088,7 +2088,7 @@
         <v>7</v>
       </c>
       <c r="X18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y18">
         <v>10</v>
@@ -2129,7 +2129,7 @@
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
         <v>9</v>
@@ -2165,7 +2165,7 @@
         <v>6</v>
       </c>
       <c r="X19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>10</v>
@@ -2206,7 +2206,7 @@
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
         <v>9</v>
@@ -2283,7 +2283,7 @@
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
         <v>10</v>
@@ -2319,7 +2319,7 @@
         <v>5</v>
       </c>
       <c r="X21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y21">
         <v>10</v>
@@ -2360,7 +2360,7 @@
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
         <v>10</v>
@@ -2437,7 +2437,7 @@
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
         <v>8</v>
@@ -2514,7 +2514,7 @@
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
         <v>8</v>
@@ -2550,7 +2550,7 @@
         <v>8</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y24">
         <v>8</v>
@@ -2591,7 +2591,7 @@
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
         <v>8</v>
@@ -2627,7 +2627,7 @@
         <v>8</v>
       </c>
       <c r="X25">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y25">
         <v>8</v>
@@ -2668,7 +2668,7 @@
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
         <v>9</v>
@@ -2704,7 +2704,7 @@
         <v>6</v>
       </c>
       <c r="X26">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y26">
         <v>9</v>
@@ -2745,7 +2745,7 @@
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M27">
         <v>9</v>
@@ -2781,7 +2781,7 @@
         <v>5</v>
       </c>
       <c r="X27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y27">
         <v>9</v>
@@ -2822,7 +2822,7 @@
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
         <v>10</v>
@@ -2858,7 +2858,7 @@
         <v>6</v>
       </c>
       <c r="X28">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y28">
         <v>10</v>
@@ -2899,7 +2899,7 @@
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
         <v>10</v>
@@ -2976,7 +2976,7 @@
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
         <v>8</v>
@@ -3053,7 +3053,7 @@
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
         <v>9</v>
@@ -3130,7 +3130,7 @@
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
         <v>8</v>
@@ -3166,7 +3166,7 @@
         <v>5</v>
       </c>
       <c r="X32">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y32">
         <v>8</v>
@@ -3207,7 +3207,7 @@
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
         <v>10</v>
@@ -3284,7 +3284,7 @@
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
         <v>10</v>
@@ -3320,7 +3320,7 @@
         <v>9</v>
       </c>
       <c r="X34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y34">
         <v>10</v>
@@ -3361,7 +3361,7 @@
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
         <v>10</v>
@@ -3488,7 +3488,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
@@ -3497,19 +3497,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>78.13</v>
+        <v>84.38</v>
       </c>
       <c r="G3">
-        <v>21.88</v>
+        <v>15.63</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>7.2</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3520,7 +3520,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
@@ -3529,30 +3529,30 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>84.38</v>
+        <v>96.88</v>
       </c>
       <c r="G4">
-        <v>15.63</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -3561,25 +3561,25 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3757,7 +3757,7 @@
         <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4482,7 +4482,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4552,7 +4552,7 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4560,22 +4560,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920297</v>
+        <v>20330051920296</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -4583,39 +4583,39 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920297</v>
+        <v>20330051920296</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920299</v>
+        <v>20330051920297</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -4629,19 +4629,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920299</v>
+        <v>20330051920297</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
         <v>54</v>
@@ -4690,7 +4690,7 @@
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4698,16 +4698,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920308</v>
+        <v>20330051920310</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -4721,19 +4721,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920308</v>
+        <v>20330051920310</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
         <v>54</v>
@@ -4744,16 +4744,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920311</v>
+        <v>20330051920284</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -4767,85 +4767,85 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920311</v>
+        <v>20330051920394</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G13">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920312</v>
+        <v>20330051920299</v>
       </c>
       <c r="B14" t="s">
-        <v>104</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="D14" t="s">
-        <v>142</v>
+        <v>85</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G14">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920312</v>
+        <v>20330051920308</v>
       </c>
       <c r="B15" t="s">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="D15" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920284</v>
+        <v>20330051920311</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
@@ -4859,47 +4859,24 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920394</v>
+        <v>20330051920312</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="C17" t="s">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="D17" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920309</v>
-      </c>
-      <c r="B18" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" t="s">
-        <v>117</v>
-      </c>
-      <c r="D18" t="s">
-        <v>139</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>54</v>
-      </c>
-      <c r="G18">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5BLCM - Estadisticos 20221.xlsx
+++ b/grupos/5BLCM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="147">
   <si>
     <t>Materia</t>
   </si>
@@ -2428,7 +2428,7 @@
         <v>8</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
         <v>7</v>
@@ -2464,7 +2464,7 @@
         <v>8</v>
       </c>
       <c r="U23">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>7</v>
@@ -2582,7 +2582,7 @@
         <v>8</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J25">
         <v>-1</v>
@@ -2618,7 +2618,7 @@
         <v>8</v>
       </c>
       <c r="U25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V25">
         <v>-1</v>
@@ -2813,7 +2813,7 @@
         <v>7</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J28">
         <v>-1</v>
@@ -2849,7 +2849,7 @@
         <v>7</v>
       </c>
       <c r="U28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V28">
         <v>-1</v>
@@ -3529,19 +3529,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>96.88</v>
+        <v>93.75</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -4482,7 +4482,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4744,39 +4744,39 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920284</v>
+        <v>20330051920311</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920394</v>
+        <v>20330051920311</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D13" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -4790,16 +4790,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920299</v>
+        <v>20330051920284</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
@@ -4813,16 +4813,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920308</v>
+        <v>20330051920394</v>
       </c>
       <c r="B15" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" t="s">
         <v>70</v>
       </c>
-      <c r="C15" t="s">
-        <v>78</v>
-      </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
@@ -4836,16 +4836,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920311</v>
+        <v>20330051920299</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D16" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
@@ -4859,24 +4859,47 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
+        <v>20330051920308</v>
+      </c>
+      <c r="B17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" t="s">
+        <v>87</v>
+      </c>
+      <c r="E17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
         <v>20330051920312</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B18" t="s">
         <v>104</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C18" t="s">
         <v>120</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D18" t="s">
         <v>142</v>
       </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
         <v>54</v>
       </c>
-      <c r="G17">
+      <c r="G18">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5BLCM - Estadisticos 20221.xlsx
+++ b/grupos/5BLCM - Estadisticos 20221.xlsx
@@ -971,7 +971,7 @@
         <v>-1</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
         <v>5</v>
@@ -1048,7 +1048,7 @@
         <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
         <v>10</v>
@@ -1125,7 +1125,7 @@
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
         <v>10</v>
@@ -1161,7 +1161,7 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -1202,7 +1202,7 @@
         <v>7</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>6</v>
@@ -1279,7 +1279,7 @@
         <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
         <v>10</v>
@@ -1315,7 +1315,7 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>10</v>
@@ -1356,7 +1356,7 @@
         <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
         <v>10</v>
@@ -1433,7 +1433,7 @@
         <v>7</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
         <v>10</v>
@@ -1469,7 +1469,7 @@
         <v>7</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1510,7 +1510,7 @@
         <v>8</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
         <v>10</v>
@@ -1587,7 +1587,7 @@
         <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
         <v>10</v>
@@ -1623,7 +1623,7 @@
         <v>8</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X12">
         <v>10</v>
@@ -1664,7 +1664,7 @@
         <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
         <v>10</v>
@@ -1700,7 +1700,7 @@
         <v>7</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X13">
         <v>10</v>
@@ -1741,7 +1741,7 @@
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
         <v>10</v>
@@ -1777,7 +1777,7 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>10</v>
@@ -1818,7 +1818,7 @@
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
         <v>7</v>
@@ -1854,7 +1854,7 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>6</v>
@@ -1895,7 +1895,7 @@
         <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
         <v>9</v>
@@ -1931,7 +1931,7 @@
         <v>8</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>10</v>
@@ -1972,7 +1972,7 @@
         <v>-1</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
         <v>10</v>
@@ -2049,7 +2049,7 @@
         <v>7</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
         <v>10</v>
@@ -2085,7 +2085,7 @@
         <v>7</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>10</v>
@@ -2126,7 +2126,7 @@
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
         <v>10</v>
@@ -2162,7 +2162,7 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>8</v>
@@ -2203,7 +2203,7 @@
         <v>7</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L20">
         <v>10</v>
@@ -2280,7 +2280,7 @@
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
         <v>10</v>
@@ -2357,7 +2357,7 @@
         <v>7</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
         <v>10</v>
@@ -2393,7 +2393,7 @@
         <v>7</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>10</v>
@@ -2434,7 +2434,7 @@
         <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
         <v>10</v>
@@ -2470,7 +2470,7 @@
         <v>7</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X23">
         <v>10</v>
@@ -2511,7 +2511,7 @@
         <v>7</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
         <v>10</v>
@@ -2547,7 +2547,7 @@
         <v>7</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>9</v>
@@ -2588,7 +2588,7 @@
         <v>-1</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
         <v>10</v>
@@ -2624,7 +2624,7 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X25">
         <v>8</v>
@@ -2665,7 +2665,7 @@
         <v>7</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
         <v>10</v>
@@ -2701,7 +2701,7 @@
         <v>7</v>
       </c>
       <c r="W26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>8</v>
@@ -2742,7 +2742,7 @@
         <v>-1</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
         <v>8</v>
@@ -2819,7 +2819,7 @@
         <v>-1</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L28">
         <v>10</v>
@@ -2855,7 +2855,7 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>8</v>
@@ -2896,7 +2896,7 @@
         <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
         <v>10</v>
@@ -2973,7 +2973,7 @@
         <v>8</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
         <v>10</v>
@@ -3050,7 +3050,7 @@
         <v>6</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L31">
         <v>10</v>
@@ -3086,7 +3086,7 @@
         <v>6</v>
       </c>
       <c r="W31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X31">
         <v>10</v>
@@ -3127,7 +3127,7 @@
         <v>7</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L32">
         <v>10</v>
@@ -3204,7 +3204,7 @@
         <v>8</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L33">
         <v>10</v>
@@ -3240,7 +3240,7 @@
         <v>8</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X33">
         <v>10</v>
@@ -3281,7 +3281,7 @@
         <v>7</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L34">
         <v>10</v>
@@ -3358,7 +3358,7 @@
         <v>8</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L35">
         <v>10</v>
@@ -3394,7 +3394,7 @@
         <v>8</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>10</v>
@@ -3509,7 +3509,7 @@
         <v>15.63</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
         <v>0</v>

--- a/grupos/5BLCM - Estadisticos 20221.xlsx
+++ b/grupos/5BLCM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="147">
   <si>
     <t>Materia</t>
   </si>
@@ -1794,7 +1794,7 @@
         <v>6</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D15">
         <v>-1</v>
@@ -1812,7 +1812,7 @@
         <v>7</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
         <v>-1</v>
@@ -1848,7 +1848,7 @@
         <v>7</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>-1</v>
@@ -2120,7 +2120,7 @@
         <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
         <v>-1</v>
@@ -2156,7 +2156,7 @@
         <v>8</v>
       </c>
       <c r="U19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V19">
         <v>-1</v>
@@ -3529,25 +3529,25 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4">
-        <v>93.75</v>
+        <v>96.88</v>
       </c>
       <c r="G4">
         <v>3.13</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3653,7 +3653,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3754,24 +3754,24 @@
         <v>83</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920296</v>
+        <v>20330051920297</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -3782,16 +3782,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920297</v>
+        <v>20330051920299</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -3802,16 +3802,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920299</v>
+        <v>20330051920301</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -3822,16 +3822,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920301</v>
+        <v>20330051920308</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -3842,16 +3842,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920308</v>
+        <v>20330051920310</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -3862,41 +3862,21 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920310</v>
+        <v>20330051920311</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920311</v>
-      </c>
-      <c r="B12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" t="s">
-        <v>89</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
         <v>53</v>
       </c>
     </row>
@@ -3933,33 +3913,33 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920296</v>
+        <v>20330051920284</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920284</v>
+        <v>20330051920286</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -3967,16 +3947,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920286</v>
+        <v>20330051920394</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -3984,16 +3964,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920394</v>
+        <v>20330051920296</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -4482,7 +4462,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4560,22 +4540,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920296</v>
+        <v>20330051920297</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -4583,39 +4563,39 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920296</v>
+        <v>20330051920297</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920297</v>
+        <v>20330051920301</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -4629,16 +4609,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920297</v>
+        <v>20330051920301</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -4652,16 +4632,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920301</v>
+        <v>20330051920310</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -4675,16 +4655,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920301</v>
+        <v>20330051920310</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -4698,85 +4678,85 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920310</v>
+        <v>20330051920311</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920310</v>
+        <v>20330051920311</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920311</v>
+        <v>20330051920284</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920311</v>
+        <v>20330051920394</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -4790,16 +4770,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920284</v>
+        <v>20330051920296</v>
       </c>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D14" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
@@ -4813,16 +4793,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920394</v>
+        <v>20330051920299</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D15" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
@@ -4836,16 +4816,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920299</v>
+        <v>20330051920308</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D16" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
@@ -4859,47 +4839,24 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920308</v>
+        <v>20330051920312</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="D17" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920312</v>
-      </c>
-      <c r="B18" t="s">
-        <v>104</v>
-      </c>
-      <c r="C18" t="s">
-        <v>120</v>
-      </c>
-      <c r="D18" t="s">
-        <v>142</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>54</v>
-      </c>
-      <c r="G18">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5BLCM - Estadisticos 20221.xlsx
+++ b/grupos/5BLCM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="147">
   <si>
     <t>Materia</t>
   </si>
@@ -179,18 +179,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
     <t>Ortega Valle Manuel</t>
   </si>
   <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
     <t>Ángel Martínez Gerson Hermenegildo</t>
   </si>
   <si>
@@ -209,238 +209,238 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
     <t>ALFONSO</t>
   </si>
   <si>
+    <t>CARAZA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GASCA</t>
+  </si>
+  <si>
+    <t>GALICIA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>HERRERA</t>
+    <t>LEYVA</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>DE LUNA</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>NAVARRO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>RAMOS</t>
   </si>
   <si>
     <t>REYES</t>
   </si>
   <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
     <t>ROJAS</t>
   </si>
   <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
     <t>OSORIO</t>
   </si>
   <si>
+    <t>CANSINO</t>
+  </si>
+  <si>
+    <t>GAMBOA</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
     <t>PRADO</t>
   </si>
   <si>
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
     <t>MONTERROSAS</t>
   </si>
   <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>PEREZ</t>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>GASPAR</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ARENZANO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>KAREN ESTEPHANY</t>
   </si>
   <si>
     <t>ISRAEL</t>
   </si>
   <si>
+    <t>CITLALLI</t>
+  </si>
+  <si>
     <t>AMERICA MICHELLE</t>
   </si>
   <si>
+    <t>JARED URIEL</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>VALERIA ANGELY</t>
+  </si>
+  <si>
+    <t>STEPHANIE</t>
+  </si>
+  <si>
+    <t>SIARI DANAHY</t>
+  </si>
+  <si>
     <t>EDUARDO</t>
   </si>
   <si>
+    <t>YAMILE</t>
+  </si>
+  <si>
     <t>ALEXA</t>
   </si>
   <si>
     <t>ARIADNA</t>
   </si>
   <si>
+    <t>ELIAN</t>
+  </si>
+  <si>
     <t>MARIA MAGDALENA</t>
   </si>
   <si>
+    <t>IKER</t>
+  </si>
+  <si>
     <t>VANESSA</t>
   </si>
   <si>
+    <t>IVONNE SHERLINE</t>
+  </si>
+  <si>
+    <t>LESLIE</t>
+  </si>
+  <si>
+    <t>RITA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
     <t>MARISOL</t>
   </si>
   <si>
+    <t>SAMANTHA</t>
+  </si>
+  <si>
     <t>ARANTZA</t>
   </si>
   <si>
+    <t>DIANA SARAY</t>
+  </si>
+  <si>
     <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>CARAZA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GASCA</t>
-  </si>
-  <si>
-    <t>GALICIA</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>DE LUNA</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>CANSINO</t>
-  </si>
-  <si>
-    <t>GAMBOA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ARENZANO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>KAREN ESTEPHANY</t>
-  </si>
-  <si>
-    <t>CITLALLI</t>
-  </si>
-  <si>
-    <t>JARED URIEL</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>VALERIA ANGELY</t>
-  </si>
-  <si>
-    <t>STEPHANIE</t>
-  </si>
-  <si>
-    <t>SIARI DANAHY</t>
-  </si>
-  <si>
-    <t>YAMILE</t>
-  </si>
-  <si>
-    <t>ELIAN</t>
-  </si>
-  <si>
-    <t>IKER</t>
-  </si>
-  <si>
-    <t>IVONNE SHERLINE</t>
-  </si>
-  <si>
-    <t>LESLIE</t>
-  </si>
-  <si>
-    <t>RITA ALEJANDRA</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>SAMANTHA</t>
-  </si>
-  <si>
-    <t>DIANA SARAY</t>
   </si>
   <si>
     <t>MARIA XIMENA</t>
@@ -950,7 +950,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -968,7 +968,7 @@
         <v>9</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
         <v>7</v>
@@ -1004,7 +1004,7 @@
         <v>8</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W4">
         <v>5</v>
@@ -1104,7 +1104,7 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E6">
         <v>7</v>
@@ -1122,7 +1122,7 @@
         <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>9</v>
@@ -1158,7 +1158,7 @@
         <v>8</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>8</v>
@@ -1720,7 +1720,7 @@
         <v>7</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E14">
         <v>6</v>
@@ -1738,7 +1738,7 @@
         <v>9</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K14">
         <v>9</v>
@@ -1774,7 +1774,7 @@
         <v>8</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W14">
         <v>8</v>
@@ -1797,7 +1797,7 @@
         <v>5</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E15">
         <v>6</v>
@@ -1815,7 +1815,7 @@
         <v>8</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
         <v>7</v>
@@ -1851,7 +1851,7 @@
         <v>7</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>7</v>
@@ -1951,7 +1951,7 @@
         <v>7</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E17">
         <v>4</v>
@@ -1969,7 +1969,7 @@
         <v>7</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
         <v>6</v>
@@ -2005,7 +2005,7 @@
         <v>7</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>5</v>
@@ -2105,7 +2105,7 @@
         <v>7</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E19">
         <v>6</v>
@@ -2123,7 +2123,7 @@
         <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
         <v>7</v>
@@ -2159,7 +2159,7 @@
         <v>6</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W19">
         <v>7</v>
@@ -2259,7 +2259,7 @@
         <v>7</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E21">
         <v>4</v>
@@ -2277,7 +2277,7 @@
         <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
         <v>6</v>
@@ -2313,7 +2313,7 @@
         <v>7</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>5</v>
@@ -2567,7 +2567,7 @@
         <v>7</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E25">
         <v>8</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K25">
         <v>9</v>
@@ -2621,7 +2621,7 @@
         <v>6</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W25">
         <v>9</v>
@@ -2721,7 +2721,7 @@
         <v>8</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E27">
         <v>4</v>
@@ -2739,7 +2739,7 @@
         <v>6</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
         <v>6</v>
@@ -2775,7 +2775,7 @@
         <v>7</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W27">
         <v>5</v>
@@ -2798,7 +2798,7 @@
         <v>6</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E28">
         <v>6</v>
@@ -2816,7 +2816,7 @@
         <v>5</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K28">
         <v>7</v>
@@ -2852,7 +2852,7 @@
         <v>5</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W28">
         <v>7</v>
@@ -3456,7 +3456,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
@@ -3465,30 +3465,30 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>68.75</v>
+        <v>84.38</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>15.63</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>31.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
@@ -3497,19 +3497,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>84.38</v>
+        <v>96.88</v>
       </c>
       <c r="G3">
-        <v>15.63</v>
+        <v>3.13</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3520,7 +3520,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
@@ -3529,19 +3529,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3552,7 +3552,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -3573,7 +3573,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9.300000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3653,7 +3653,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3678,206 +3678,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920284</v>
-      </c>
-      <c r="B2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920286</v>
-      </c>
-      <c r="B3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920394</v>
-      </c>
-      <c r="B4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920296</v>
-      </c>
-      <c r="B5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920297</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D6" t="s">
-        <v>84</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920299</v>
-      </c>
-      <c r="B7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7" t="s">
-        <v>85</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920301</v>
-      </c>
-      <c r="B8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" t="s">
-        <v>86</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920308</v>
-      </c>
-      <c r="B9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" t="s">
-        <v>87</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920310</v>
-      </c>
-      <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920311</v>
-      </c>
-      <c r="B11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11" t="s">
-        <v>89</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -3913,183 +3713,183 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920284</v>
+        <v>20330051920283</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920286</v>
+        <v>20330051920284</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920394</v>
+        <v>20330051920285</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920296</v>
+        <v>20330051920286</v>
       </c>
       <c r="B5" t="s">
         <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920297</v>
+        <v>20330051920390</v>
       </c>
       <c r="B6" t="s">
         <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920299</v>
+        <v>20330051920290</v>
       </c>
       <c r="B7" t="s">
         <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920301</v>
+        <v>20330051920292</v>
       </c>
       <c r="B8" t="s">
         <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920308</v>
+        <v>20330051920293</v>
       </c>
       <c r="B9" t="s">
         <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920310</v>
+        <v>20330051920294</v>
       </c>
       <c r="B10" t="s">
         <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920311</v>
+        <v>20330051920394</v>
       </c>
       <c r="B11" t="s">
         <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920283</v>
+        <v>20330051920295</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="D12" t="s">
         <v>125</v>
@@ -4100,13 +3900,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920285</v>
+        <v>20330051920296</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
         <v>126</v>
@@ -4117,13 +3917,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920390</v>
+        <v>20330051920297</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
         <v>127</v>
@@ -4134,13 +3934,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920290</v>
+        <v>20330051920298</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
         <v>128</v>
@@ -4151,13 +3951,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920292</v>
+        <v>20330051920299</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
         <v>129</v>
@@ -4168,13 +3968,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920293</v>
+        <v>20330051920300</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
         <v>130</v>
@@ -4185,13 +3985,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920294</v>
+        <v>20330051920301</v>
       </c>
       <c r="B18" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="D18" t="s">
         <v>131</v>
@@ -4202,13 +4002,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920295</v>
+        <v>20330051920303</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
         <v>132</v>
@@ -4219,13 +4019,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920298</v>
+        <v>20330051920208</v>
       </c>
       <c r="B20" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="D20" t="s">
         <v>133</v>
@@ -4236,13 +4036,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920300</v>
+        <v>20330051920304</v>
       </c>
       <c r="B21" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="D21" t="s">
         <v>134</v>
@@ -4253,13 +4053,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920303</v>
+        <v>20330051920307</v>
       </c>
       <c r="B22" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D22" t="s">
         <v>135</v>
@@ -4270,13 +4070,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920208</v>
+        <v>20330051920308</v>
       </c>
       <c r="B23" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="D23" t="s">
         <v>136</v>
@@ -4287,13 +4087,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920304</v>
+        <v>20330051920309</v>
       </c>
       <c r="B24" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C24" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D24" t="s">
         <v>137</v>
@@ -4304,13 +4104,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920307</v>
+        <v>20330051920310</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="D25" t="s">
         <v>138</v>
@@ -4321,13 +4121,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920309</v>
+        <v>20330051920211</v>
       </c>
       <c r="B26" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="D26" t="s">
         <v>139</v>
@@ -4338,13 +4138,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920211</v>
+        <v>20330051920311</v>
       </c>
       <c r="B27" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="D27" t="s">
         <v>140</v>
@@ -4358,10 +4158,10 @@
         <v>20330051920216</v>
       </c>
       <c r="B28" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="D28" t="s">
         <v>141</v>
@@ -4375,10 +4175,10 @@
         <v>20330051920312</v>
       </c>
       <c r="B29" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D29" t="s">
         <v>142</v>
@@ -4392,10 +4192,10 @@
         <v>20330051920379</v>
       </c>
       <c r="B30" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="D30" t="s">
         <v>143</v>
@@ -4409,10 +4209,10 @@
         <v>20330051920313</v>
       </c>
       <c r="B31" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="C31" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D31" t="s">
         <v>144</v>
@@ -4426,10 +4226,10 @@
         <v>20330051920314</v>
       </c>
       <c r="B32" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="C32" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="D32" t="s">
         <v>145</v>
@@ -4443,10 +4243,10 @@
         <v>20330051920316</v>
       </c>
       <c r="B33" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="C33" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D33" t="s">
         <v>146</v>
@@ -4462,7 +4262,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4497,42 +4297,42 @@
         <v>20330051920286</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
         <v>53</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920286</v>
+        <v>20330051920297</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4540,45 +4340,45 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920297</v>
+        <v>20330051920301</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
         <v>53</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920297</v>
+        <v>20330051920310</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4586,277 +4386,47 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920301</v>
+        <v>20330051920311</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>140</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920301</v>
+        <v>20330051920312</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>142</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920310</v>
-      </c>
-      <c r="B8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D8" t="s">
-        <v>88</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920310</v>
-      </c>
-      <c r="B9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D9" t="s">
-        <v>88</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920311</v>
-      </c>
-      <c r="B10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" t="s">
-        <v>89</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920311</v>
-      </c>
-      <c r="B11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11" t="s">
-        <v>89</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>53</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920284</v>
-      </c>
-      <c r="B12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D12" t="s">
-        <v>80</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920394</v>
-      </c>
-      <c r="B13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" t="s">
-        <v>70</v>
-      </c>
-      <c r="D13" t="s">
-        <v>82</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920296</v>
-      </c>
-      <c r="B14" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" t="s">
-        <v>83</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920299</v>
-      </c>
-      <c r="B15" t="s">
-        <v>68</v>
-      </c>
-      <c r="C15" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" t="s">
-        <v>85</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920308</v>
-      </c>
-      <c r="B16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" t="s">
-        <v>78</v>
-      </c>
-      <c r="D16" t="s">
-        <v>87</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>53</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920312</v>
-      </c>
-      <c r="B17" t="s">
-        <v>104</v>
-      </c>
-      <c r="C17" t="s">
-        <v>120</v>
-      </c>
-      <c r="D17" t="s">
-        <v>142</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>54</v>
-      </c>
-      <c r="G17">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5BLCM - Estadisticos 20221.xlsx
+++ b/grupos/5BLCM - Estadisticos 20221.xlsx
@@ -980,7 +980,7 @@
         <v>7</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -995,10 +995,10 @@
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U4">
         <v>8</v>
@@ -1013,7 +1013,7 @@
         <v>7</v>
       </c>
       <c r="Y4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1057,7 +1057,7 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -1072,7 +1072,7 @@
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>10</v>
@@ -1134,7 +1134,7 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -1149,7 +1149,7 @@
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>9</v>
@@ -1211,7 +1211,7 @@
         <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -1226,7 +1226,7 @@
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>7</v>
@@ -1288,7 +1288,7 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -1303,7 +1303,7 @@
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>8</v>
@@ -1365,7 +1365,7 @@
         <v>10</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -1380,7 +1380,7 @@
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -1442,7 +1442,7 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
         <v>-1</v>
@@ -1457,7 +1457,7 @@
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>8</v>
@@ -1519,7 +1519,7 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -1534,7 +1534,7 @@
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -1596,7 +1596,7 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -1611,7 +1611,7 @@
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>9</v>
@@ -1673,7 +1673,7 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -1688,7 +1688,7 @@
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>10</v>
@@ -1750,7 +1750,7 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -1765,10 +1765,10 @@
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U14">
         <v>8</v>
@@ -1827,7 +1827,7 @@
         <v>8</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -1842,10 +1842,10 @@
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U15">
         <v>7</v>
@@ -1860,7 +1860,7 @@
         <v>6</v>
       </c>
       <c r="Y15">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1904,7 +1904,7 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -1919,10 +1919,10 @@
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U16">
         <v>9</v>
@@ -1937,7 +1937,7 @@
         <v>10</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1981,7 +1981,7 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
         <v>-1</v>
@@ -1996,10 +1996,10 @@
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>7</v>
@@ -2014,7 +2014,7 @@
         <v>10</v>
       </c>
       <c r="Y17">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2058,7 +2058,7 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -2073,7 +2073,7 @@
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>9</v>
@@ -2135,7 +2135,7 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -2150,10 +2150,10 @@
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U19">
         <v>6</v>
@@ -2168,7 +2168,7 @@
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2212,7 +2212,7 @@
         <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -2227,7 +2227,7 @@
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
         <v>9</v>
@@ -2289,7 +2289,7 @@
         <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -2304,10 +2304,10 @@
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U21">
         <v>7</v>
@@ -2322,7 +2322,7 @@
         <v>10</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2366,7 +2366,7 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -2381,7 +2381,7 @@
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>9</v>
@@ -2443,7 +2443,7 @@
         <v>8</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
         <v>-1</v>
@@ -2458,10 +2458,10 @@
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U23">
         <v>6</v>
@@ -2476,7 +2476,7 @@
         <v>10</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2520,7 +2520,7 @@
         <v>8</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
         <v>-1</v>
@@ -2535,7 +2535,7 @@
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>10</v>
@@ -2597,7 +2597,7 @@
         <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
         <v>-1</v>
@@ -2612,7 +2612,7 @@
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
         <v>8</v>
@@ -2674,7 +2674,7 @@
         <v>9</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O26">
         <v>-1</v>
@@ -2689,7 +2689,7 @@
         <v>-1</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
         <v>7</v>
@@ -2751,7 +2751,7 @@
         <v>9</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
         <v>-1</v>
@@ -2766,10 +2766,10 @@
         <v>-1</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U27">
         <v>7</v>
@@ -2784,7 +2784,7 @@
         <v>7</v>
       </c>
       <c r="Y27">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2828,7 +2828,7 @@
         <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
         <v>-1</v>
@@ -2843,7 +2843,7 @@
         <v>-1</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
         <v>7</v>
@@ -2861,7 +2861,7 @@
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2905,7 +2905,7 @@
         <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
         <v>-1</v>
@@ -2920,7 +2920,7 @@
         <v>-1</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>9</v>
@@ -2982,7 +2982,7 @@
         <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O30">
         <v>-1</v>
@@ -2997,10 +2997,10 @@
         <v>-1</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U30">
         <v>8</v>
@@ -3059,7 +3059,7 @@
         <v>9</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O31">
         <v>-1</v>
@@ -3074,10 +3074,10 @@
         <v>-1</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U31">
         <v>9</v>
@@ -3136,7 +3136,7 @@
         <v>8</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O32">
         <v>-1</v>
@@ -3151,10 +3151,10 @@
         <v>-1</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U32">
         <v>7</v>
@@ -3213,7 +3213,7 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
         <v>-1</v>
@@ -3228,7 +3228,7 @@
         <v>-1</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -3290,7 +3290,7 @@
         <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
         <v>-1</v>
@@ -3305,7 +3305,7 @@
         <v>-1</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>10</v>
@@ -3367,7 +3367,7 @@
         <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
         <v>-1</v>
@@ -3382,7 +3382,7 @@
         <v>-1</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
         <v>10</v>
@@ -3605,7 +3605,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3637,7 +3637,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/5BLCM - Estadisticos 20221.xlsx
+++ b/grupos/5BLCM - Estadisticos 20221.xlsx
@@ -983,10 +983,10 @@
         <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
         <v>-1</v>
@@ -1004,7 +1004,7 @@
         <v>8</v>
       </c>
       <c r="V4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>5</v>
@@ -1060,10 +1060,10 @@
         <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
         <v>-1</v>
@@ -1137,10 +1137,10 @@
         <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
         <v>-1</v>
@@ -1155,10 +1155,10 @@
         <v>9</v>
       </c>
       <c r="U6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>8</v>
@@ -1214,10 +1214,10 @@
         <v>8</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
         <v>-1</v>
@@ -1232,7 +1232,7 @@
         <v>7</v>
       </c>
       <c r="U7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>7</v>
@@ -1291,10 +1291,10 @@
         <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
         <v>-1</v>
@@ -1312,7 +1312,7 @@
         <v>9</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1368,10 +1368,10 @@
         <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
         <v>-1</v>
@@ -1389,7 +1389,7 @@
         <v>9</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>10</v>
@@ -1445,10 +1445,10 @@
         <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
         <v>-1</v>
@@ -1463,10 +1463,10 @@
         <v>8</v>
       </c>
       <c r="U10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>8</v>
@@ -1522,10 +1522,10 @@
         <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
         <v>-1</v>
@@ -1540,7 +1540,7 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V11">
         <v>8</v>
@@ -1599,10 +1599,10 @@
         <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
         <v>-1</v>
@@ -1676,10 +1676,10 @@
         <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
         <v>-1</v>
@@ -1694,7 +1694,7 @@
         <v>10</v>
       </c>
       <c r="U13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V13">
         <v>7</v>
@@ -1753,10 +1753,10 @@
         <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
         <v>-1</v>
@@ -1771,10 +1771,10 @@
         <v>8</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>8</v>
@@ -1830,10 +1830,10 @@
         <v>5</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
         <v>-1</v>
@@ -1848,7 +1848,7 @@
         <v>6</v>
       </c>
       <c r="U15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V15">
         <v>6</v>
@@ -1907,10 +1907,10 @@
         <v>8</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
         <v>-1</v>
@@ -1984,10 +1984,10 @@
         <v>7</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
         <v>-1</v>
@@ -2061,10 +2061,10 @@
         <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
         <v>-1</v>
@@ -2082,7 +2082,7 @@
         <v>8</v>
       </c>
       <c r="V18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>8</v>
@@ -2138,10 +2138,10 @@
         <v>7</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
         <v>-1</v>
@@ -2215,10 +2215,10 @@
         <v>9</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
         <v>-1</v>
@@ -2236,7 +2236,7 @@
         <v>8</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W20">
         <v>9</v>
@@ -2292,10 +2292,10 @@
         <v>8</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q21">
         <v>-1</v>
@@ -2313,7 +2313,7 @@
         <v>7</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>5</v>
@@ -2369,10 +2369,10 @@
         <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
         <v>-1</v>
@@ -2390,7 +2390,7 @@
         <v>9</v>
       </c>
       <c r="V22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>8</v>
@@ -2446,10 +2446,10 @@
         <v>7</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
         <v>-1</v>
@@ -2467,7 +2467,7 @@
         <v>6</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W23">
         <v>9</v>
@@ -2523,10 +2523,10 @@
         <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
         <v>-1</v>
@@ -2541,10 +2541,10 @@
         <v>10</v>
       </c>
       <c r="U24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W24">
         <v>9</v>
@@ -2600,10 +2600,10 @@
         <v>8</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
         <v>-1</v>
@@ -2618,7 +2618,7 @@
         <v>8</v>
       </c>
       <c r="U25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V25">
         <v>7</v>
@@ -2677,10 +2677,10 @@
         <v>9</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
         <v>-1</v>
@@ -2754,10 +2754,10 @@
         <v>8</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
         <v>-1</v>
@@ -2831,10 +2831,10 @@
         <v>8</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q28">
         <v>-1</v>
@@ -2908,10 +2908,10 @@
         <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
         <v>-1</v>
@@ -2929,7 +2929,7 @@
         <v>9</v>
       </c>
       <c r="V29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W29">
         <v>9</v>
@@ -2985,10 +2985,10 @@
         <v>8</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
         <v>-1</v>
@@ -3062,10 +3062,10 @@
         <v>9</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q31">
         <v>-1</v>
@@ -3083,7 +3083,7 @@
         <v>9</v>
       </c>
       <c r="V31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W31">
         <v>8</v>
@@ -3139,10 +3139,10 @@
         <v>8</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q32">
         <v>-1</v>
@@ -3216,10 +3216,10 @@
         <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
         <v>-1</v>
@@ -3234,7 +3234,7 @@
         <v>10</v>
       </c>
       <c r="U33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V33">
         <v>8</v>
@@ -3293,10 +3293,10 @@
         <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q34">
         <v>-1</v>
@@ -3314,7 +3314,7 @@
         <v>9</v>
       </c>
       <c r="V34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W34">
         <v>9</v>
@@ -3370,10 +3370,10 @@
         <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q35">
         <v>-1</v>
@@ -3391,7 +3391,7 @@
         <v>9</v>
       </c>
       <c r="V35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W35">
         <v>9</v>
@@ -3573,7 +3573,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
         <v>0</v>

--- a/grupos/5BLCM - Estadisticos 20221.xlsx
+++ b/grupos/5BLCM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="147">
   <si>
     <t>Materia</t>
   </si>
@@ -179,13 +179,13 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
     <t>Ortega Valle Manuel</t>
@@ -989,10 +989,10 @@
         <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
         <v>10</v>
@@ -1066,10 +1066,10 @@
         <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
         <v>10</v>
@@ -1084,7 +1084,7 @@
         <v>8</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X5">
         <v>10</v>
@@ -1143,10 +1143,10 @@
         <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
         <v>10</v>
@@ -1220,10 +1220,10 @@
         <v>7</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
         <v>8</v>
@@ -1297,10 +1297,10 @@
         <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
         <v>10</v>
@@ -1374,10 +1374,10 @@
         <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
         <v>10</v>
@@ -1451,10 +1451,10 @@
         <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
         <v>10</v>
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
         <v>10</v>
@@ -1546,7 +1546,7 @@
         <v>8</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -1605,10 +1605,10 @@
         <v>8</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
         <v>10</v>
@@ -1682,10 +1682,10 @@
         <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
         <v>9</v>
@@ -1700,7 +1700,7 @@
         <v>7</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>10</v>
@@ -1759,10 +1759,10 @@
         <v>8</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
         <v>10</v>
@@ -1836,10 +1836,10 @@
         <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
         <v>5</v>
@@ -1854,7 +1854,7 @@
         <v>6</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>6</v>
@@ -1913,10 +1913,10 @@
         <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
         <v>8</v>
@@ -1931,10 +1931,10 @@
         <v>8</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y16">
         <v>9</v>
@@ -1990,10 +1990,10 @@
         <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
         <v>7</v>
@@ -2008,7 +2008,7 @@
         <v>7</v>
       </c>
       <c r="W17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X17">
         <v>10</v>
@@ -2067,10 +2067,10 @@
         <v>9</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
         <v>10</v>
@@ -2085,10 +2085,10 @@
         <v>8</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y18">
         <v>10</v>
@@ -2144,10 +2144,10 @@
         <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S19">
         <v>6</v>
@@ -2162,10 +2162,10 @@
         <v>6</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -2221,10 +2221,10 @@
         <v>9</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
         <v>9</v>
@@ -2239,7 +2239,7 @@
         <v>8</v>
       </c>
       <c r="W20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X20">
         <v>10</v>
@@ -2298,10 +2298,10 @@
         <v>6</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S21">
         <v>8</v>
@@ -2316,10 +2316,10 @@
         <v>6</v>
       </c>
       <c r="W21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>9</v>
@@ -2375,10 +2375,10 @@
         <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
         <v>10</v>
@@ -2452,10 +2452,10 @@
         <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
         <v>5</v>
@@ -2470,7 +2470,7 @@
         <v>8</v>
       </c>
       <c r="W23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>10</v>
@@ -2529,10 +2529,10 @@
         <v>9</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
         <v>10</v>
@@ -2606,10 +2606,10 @@
         <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S25">
         <v>8</v>
@@ -2624,10 +2624,10 @@
         <v>7</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y25">
         <v>8</v>
@@ -2683,10 +2683,10 @@
         <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
         <v>9</v>
@@ -2701,7 +2701,7 @@
         <v>7</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>8</v>
@@ -2760,10 +2760,10 @@
         <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S27">
         <v>8</v>
@@ -2778,10 +2778,10 @@
         <v>7</v>
       </c>
       <c r="W27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y27">
         <v>8</v>
@@ -2837,10 +2837,10 @@
         <v>6</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
         <v>8</v>
@@ -2914,10 +2914,10 @@
         <v>10</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
         <v>10</v>
@@ -2932,7 +2932,7 @@
         <v>9</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X29">
         <v>10</v>
@@ -2991,10 +2991,10 @@
         <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
         <v>8</v>
@@ -3009,7 +3009,7 @@
         <v>8</v>
       </c>
       <c r="W30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X30">
         <v>10</v>
@@ -3068,10 +3068,10 @@
         <v>8</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
         <v>9</v>
@@ -3145,10 +3145,10 @@
         <v>6</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S32">
         <v>8</v>
@@ -3163,10 +3163,10 @@
         <v>7</v>
       </c>
       <c r="W32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y32">
         <v>8</v>
@@ -3222,10 +3222,10 @@
         <v>9</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
         <v>10</v>
@@ -3240,7 +3240,7 @@
         <v>8</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X33">
         <v>10</v>
@@ -3299,10 +3299,10 @@
         <v>9</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
         <v>10</v>
@@ -3317,7 +3317,7 @@
         <v>8</v>
       </c>
       <c r="W34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X34">
         <v>10</v>
@@ -3376,10 +3376,10 @@
         <v>10</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
         <v>10</v>
@@ -3456,7 +3456,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
@@ -3465,19 +3465,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>84.38</v>
+        <v>96.88</v>
       </c>
       <c r="G2">
-        <v>15.63</v>
+        <v>3.13</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>8.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3520,7 +3520,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
@@ -3529,19 +3529,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>100</v>
+        <v>96.88</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="H4">
-        <v>9.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4262,7 +4262,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4309,7 +4309,7 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4317,19 +4317,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920297</v>
+        <v>20330051920308</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D3" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
         <v>53</v>
@@ -4340,93 +4340,24 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920301</v>
+        <v>20330051920311</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920310</v>
-      </c>
-      <c r="B5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D5" t="s">
-        <v>138</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920311</v>
-      </c>
-      <c r="B6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C6" t="s">
-        <v>86</v>
-      </c>
-      <c r="D6" t="s">
-        <v>140</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>54</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920312</v>
-      </c>
-      <c r="B7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D7" t="s">
-        <v>142</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G7">
         <v>5</v>
       </c>
     </row>
